--- a/Unit_Test_Plan_IRCTC_IVR.xlsx
+++ b/Unit_Test_Plan_IRCTC_IVR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ad8e6a89a6abcdc6/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ad8e6a89a6abcdc6/Desktop/Infosys/IRCTC-Conversational-IVR-Modernization-Framework/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{8960B664-49BE-49BA-87E4-D44BAB643FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A66F8CF0-608A-473D-B3FA-BE7DAB1994CF}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{8960B664-49BE-49BA-87E4-D44BAB643FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{509405F1-90F6-4EB2-801C-DC3CD0C09421}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="88">
   <si>
     <t>Sl No</t>
   </si>
@@ -52,9 +52,6 @@
     <t>session_id not in sessions dict</t>
   </si>
   <si>
-    <t>Returns welcome text and creates sessions[session_id] = {'state':'menu'}</t>
-  </si>
-  <si>
     <t>Session created; welcome message returned</t>
   </si>
   <si>
@@ -64,211 +61,229 @@
     <t>Menu Option 1 – Booking Flow</t>
   </si>
   <si>
-    <t>POST /ivr with input='1' on active menu session</t>
-  </si>
-  <si>
-    <t>state == 'menu', user_input == '1'</t>
-  </si>
-  <si>
-    <t>State changes to 'source'; returns 'Please enter Source Station code'</t>
-  </si>
-  <si>
-    <t>State set to source; correct prompt returned</t>
-  </si>
-  <si>
     <t>Menu Option 2 – PNR Flow</t>
   </si>
   <si>
-    <t>POST /ivr with input='2' on active menu session</t>
-  </si>
-  <si>
-    <t>state == 'menu', user_input == '2'</t>
-  </si>
-  <si>
-    <t>State changes to 'pnr'; returns 'Please enter your 10 digit PNR number'</t>
-  </si>
-  <si>
-    <t>State set to pnr; PNR prompt returned</t>
-  </si>
-  <si>
-    <t>Menu Option 3 – Cancel Flow</t>
-  </si>
-  <si>
-    <t>POST /ivr with input='3' on active menu session</t>
-  </si>
-  <si>
-    <t>state == 'menu', user_input == '3'</t>
-  </si>
-  <si>
-    <t>State changes to 'cancel'; returns 'Please enter your PNR number to cancel'</t>
-  </si>
-  <si>
-    <t>State set to cancel; correct prompt returned</t>
-  </si>
-  <si>
-    <t>Menu Option 4 – Availability Flow</t>
-  </si>
-  <si>
-    <t>POST /ivr with input='4' on active menu session</t>
-  </si>
-  <si>
-    <t>state == 'menu', user_input == '4'</t>
-  </si>
-  <si>
-    <t>State changes to 'availability'; returns 'Please enter Train Number'</t>
-  </si>
-  <si>
-    <t>Availability prompt returned correctly</t>
-  </si>
-  <si>
     <t>Menu Option 5 – Customer Care</t>
   </si>
   <si>
-    <t>POST /ivr with input='5' on active menu session</t>
-  </si>
-  <si>
-    <t>state == 'menu', user_input == '5'</t>
-  </si>
-  <si>
-    <t>Returns agent connection message and resets state to menu</t>
-  </si>
-  <si>
-    <t>Agent message returned; state reset to menu</t>
-  </si>
-  <si>
-    <t>Voice Keyword: 'pnr'</t>
-  </si>
-  <si>
-    <t>Call detect_voice_option('check my pnr status')</t>
-  </si>
-  <si>
-    <t>Input contains 'pnr'</t>
-  </si>
-  <si>
-    <t>Returns '2'</t>
-  </si>
-  <si>
-    <t>Voice Keyword: 'book'</t>
-  </si>
-  <si>
-    <t>Call detect_voice_option('i want to book a ticket')</t>
-  </si>
-  <si>
-    <t>Input contains 'book'</t>
-  </si>
-  <si>
-    <t>Returns '1'</t>
-  </si>
-  <si>
-    <t>Voice Keyword: 'cancel'</t>
-  </si>
-  <si>
-    <t>Call detect_voice_option('cancel my booking')</t>
-  </si>
-  <si>
-    <t>Input contains 'cancel'</t>
-  </si>
-  <si>
-    <t>Returns '3'</t>
-  </si>
-  <si>
-    <t>Voice Keyword: 'availability'</t>
-  </si>
-  <si>
-    <t>Call detect_voice_option('check train availability')</t>
-  </si>
-  <si>
-    <t>Input contains 'availability'</t>
-  </si>
-  <si>
-    <t>Returns '4'</t>
-  </si>
-  <si>
-    <t>Voice Keyword: 'agent'</t>
-  </si>
-  <si>
-    <t>Call detect_voice_option('connect me to customer care')</t>
-  </si>
-  <si>
-    <t>Input contains 'customer care'</t>
-  </si>
-  <si>
-    <t>Returns '5'</t>
-  </si>
-  <si>
-    <t>Voice Keyword: Unknown Input</t>
-  </si>
-  <si>
-    <t>Call detect_voice_option('what is the weather')</t>
-  </si>
-  <si>
-    <t>No matching keyword</t>
-  </si>
-  <si>
-    <t>Returns original input unchanged</t>
-  </si>
-  <si>
-    <t>Original string returned unchanged</t>
-  </si>
-  <si>
-    <t>Session Reset via /reset</t>
-  </si>
-  <si>
-    <t>POST /reset with existing session_id</t>
-  </si>
-  <si>
-    <t>session_id exists in sessions</t>
-  </si>
-  <si>
-    <t>Session deleted; returns {'message': 'Session reset successful'}</t>
-  </si>
-  <si>
-    <t>Session removed; success message returned</t>
-  </si>
-  <si>
-    <t>Start Button Visibility</t>
-  </si>
-  <si>
-    <t>Load index.html and check IVR card state</t>
-  </si>
-  <si>
-    <t>Page loads in browser</t>
-  </si>
-  <si>
-    <t>IVR card is immediately visible; no start button present</t>
-  </si>
-  <si>
-    <t>IVR card visible on load</t>
-  </si>
-  <si>
-    <t>TTS Mutes Microphone During Playback</t>
-  </si>
-  <si>
-    <t>Trigger TTS response; check mic state</t>
-  </si>
-  <si>
-    <t>isSpeaking = true during speech synthesis</t>
-  </si>
-  <si>
-    <t>recognition.stop() called before TTS; mic does not capture bot voice</t>
-  </si>
-  <si>
-    <t>Mic muted; no self-hearing loop observed</t>
-  </si>
-  <si>
-    <t>Voice Auto-Restart After TTS</t>
-  </si>
-  <si>
-    <t>Wait for TTS to complete; check mic state</t>
-  </si>
-  <si>
-    <t>isSpeaking = false after speech.onend fires</t>
-  </si>
-  <si>
-    <t>startVoice() called 800ms after TTS ends; recognition.start() fires</t>
-  </si>
-  <si>
-    <t>Mic restarts after TTS with 800ms delay</t>
+    <t>Returns welcome text and creates session</t>
+  </si>
+  <si>
+    <t>Input "book ticket" or "1" at menu</t>
+  </si>
+  <si>
+    <t>Intent = booking</t>
+  </si>
+  <si>
+    <t>State changes to booking flow</t>
+  </si>
+  <si>
+    <t>Booking flow started correctly</t>
+  </si>
+  <si>
+    <t>Input "check pnr status" or "2" at menu</t>
+  </si>
+  <si>
+    <t>Intent = pnr_status</t>
+  </si>
+  <si>
+    <t>System asks for PNR number</t>
+  </si>
+  <si>
+    <t>Correct PNR prompt returned</t>
+  </si>
+  <si>
+    <t>Menu Option 3 – Cancel Ticket</t>
+  </si>
+  <si>
+    <t>Input "cancel ticket" or "3" at menu</t>
+  </si>
+  <si>
+    <t>Intent = cancel_ticket</t>
+  </si>
+  <si>
+    <t>System asks for booking ID</t>
+  </si>
+  <si>
+    <t>Cancel flow triggered correctly</t>
+  </si>
+  <si>
+    <t>Menu Option 4 – Train Availability</t>
+  </si>
+  <si>
+    <t>Input "train availability" or "4" at menu</t>
+  </si>
+  <si>
+    <t>Intent = availability</t>
+  </si>
+  <si>
+    <t>System asks for train details</t>
+  </si>
+  <si>
+    <t>Availability flow working</t>
+  </si>
+  <si>
+    <t>Input "talk to agent" or "5" at menu</t>
+  </si>
+  <si>
+    <t>Intent = agent</t>
+  </si>
+  <si>
+    <t>System responds with connecting message</t>
+  </si>
+  <si>
+    <t>Agent message shown; returns to menu</t>
+  </si>
+  <si>
+    <t>Voice Input Recognition</t>
+  </si>
+  <si>
+    <t>Use mic and speak command</t>
+  </si>
+  <si>
+    <t>Voice converted to text</t>
+  </si>
+  <si>
+    <t>Text correctly captured</t>
+  </si>
+  <si>
+    <t>Text matches spoken input</t>
+  </si>
+  <si>
+    <t>Voice Intent Detection</t>
+  </si>
+  <si>
+    <t>Speak "check pnr status"</t>
+  </si>
+  <si>
+    <t>Intent detection runs</t>
+  </si>
+  <si>
+    <t>Returns correct intent (pnr_status)</t>
+  </si>
+  <si>
+    <t>Intent correctly detected</t>
+  </si>
+  <si>
+    <t>Continuous Voice Listening</t>
+  </si>
+  <si>
+    <t>Speak multiple commands continuously</t>
+  </si>
+  <si>
+    <t>Recognition auto-restarts</t>
+  </si>
+  <si>
+    <t>System keeps listening after response</t>
+  </si>
+  <si>
+    <t>Continuous listening working</t>
+  </si>
+  <si>
+    <t>TTS Output</t>
+  </si>
+  <si>
+    <t>Response generated by system</t>
+  </si>
+  <si>
+    <t>Text-to-Speech triggered</t>
+  </si>
+  <si>
+    <t>System speaks response clearly</t>
+  </si>
+  <si>
+    <t>Audio output working</t>
+  </si>
+  <si>
+    <t>TTS Mic Blocking</t>
+  </si>
+  <si>
+    <t>During speech output</t>
+  </si>
+  <si>
+    <t>isSpeaking = true</t>
+  </si>
+  <si>
+    <t>Mic disabled during speech</t>
+  </si>
+  <si>
+    <t>No self-hearing issue</t>
+  </si>
+  <si>
+    <t>Voice Restart After TTS</t>
+  </si>
+  <si>
+    <t>After speech ends</t>
+  </si>
+  <si>
+    <t>isSpeaking = false</t>
+  </si>
+  <si>
+    <t>Mic restarts automatically</t>
+  </si>
+  <si>
+    <t>Voice resumes correctly</t>
+  </si>
+  <si>
+    <t>Start Screen Navigation</t>
+  </si>
+  <si>
+    <t>Click "Get Started" button</t>
+  </si>
+  <si>
+    <t>User interaction triggered</t>
+  </si>
+  <si>
+    <t>IVR interface loads</t>
+  </si>
+  <si>
+    <t>Navigation works correctly</t>
+  </si>
+  <si>
+    <t>Auto Welcome Message</t>
+  </si>
+  <si>
+    <t>IVR loads after start button</t>
+  </si>
+  <si>
+    <t>System triggers API call</t>
+  </si>
+  <si>
+    <t>Welcome message displayed and spoken</t>
+  </si>
+  <si>
+    <t>Auto-start working</t>
+  </si>
+  <si>
+    <t>Cancel Ticket Voice Fix</t>
+  </si>
+  <si>
+    <t>Speak "cancel my ticket"</t>
+  </si>
+  <si>
+    <t>Intent detection fixed</t>
+  </si>
+  <si>
+    <t>Routes to cancel flow</t>
+  </si>
+  <si>
+    <t>Correct flow triggered</t>
+  </si>
+  <si>
+    <t>Invalid Input Handling</t>
+  </si>
+  <si>
+    <t>Input unknown text</t>
+  </si>
+  <si>
+    <t>No matching intent</t>
+  </si>
+  <si>
+    <t>System responds with fallback</t>
+  </si>
+  <si>
+    <t>Response handled properly</t>
   </si>
 </sst>
 </file>
@@ -296,7 +311,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -313,12 +328,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F8FF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF0F8FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -349,15 +358,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -656,7 +662,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -670,358 +676,358 @@
         <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="G7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="B15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
